--- a/outputs/staging/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
+++ b/outputs/staging/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="376" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="382" uniqueCount="118">
   <si>
     <t>field</t>
   </si>
@@ -30,10 +30,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Target year</t>
-  </si>
-  <si>
-    <t>Baseline period</t>
+    <t>Output type</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Surveillance area</t>
   </si>
   <si>
     <t>Registry</t>
@@ -42,6 +45,12 @@
     <t>Geography</t>
   </si>
   <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Release date</t>
+  </si>
+  <si>
     <t>Contents</t>
   </si>
   <si>
@@ -57,28 +66,37 @@
     <t>cvd_los_2023_v1</t>
   </si>
   <si>
-    <t>Hospital cardiovascular length of stay in Barbados, 2023</t>
+    <t>Barbados CVD length of stay, 2010-2023</t>
+  </si>
+  <si>
+    <t>briefing</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>CVD</t>
+  </si>
+  <si>
+    <t>BNR-CVD</t>
+  </si>
+  <si>
+    <t>Barbados</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2010-2021</t>
-  </si>
-  <si>
-    <t>BNR-CVD</t>
-  </si>
-  <si>
-    <t>Barbados</t>
+    <t>2026-05-15</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
   </si>
   <si>
-    <t>Aggregate hospital-ascertained length of stay</t>
-  </si>
-  <si>
-    <t>length of stay based on hospital cases</t>
+    <t>Aggregate hospital-ascertained length-of-stay and bed-day demand outputs.</t>
+  </si>
+  <si>
+    <t>Length of stay is based on hospital-ascertained CVD events only.</t>
   </si>
   <si>
     <t>indicator</t>
@@ -400,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -408,7 +426,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -416,7 +434,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +442,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -432,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -440,7 +458,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +466,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -456,7 +474,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +482,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -472,7 +490,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -480,7 +498,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -494,34 +536,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -529,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1">
         <v>6</v>
@@ -561,13 +603,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1">
         <v>6</v>
@@ -593,13 +635,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1">
         <v>7</v>
@@ -625,13 +667,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1">
         <v>6</v>
@@ -657,13 +699,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
@@ -689,13 +731,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
         <v>7</v>
@@ -721,13 +763,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
@@ -753,13 +795,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
@@ -785,13 +827,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
@@ -817,13 +859,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1">
         <v>7</v>
@@ -849,13 +891,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
@@ -881,13 +923,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
@@ -913,13 +955,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
@@ -945,13 +987,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1">
         <v>5</v>
@@ -977,13 +1019,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
@@ -1009,13 +1051,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
@@ -1041,13 +1083,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
@@ -1073,13 +1115,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
@@ -1111,200 +1153,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1318,255 +1360,255 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1580,34 +1622,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
@@ -1615,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1">
         <v>2014</v>
@@ -1647,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1">
         <v>2015</v>
@@ -1679,7 +1721,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1">
         <v>2016</v>
@@ -1711,7 +1753,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1">
         <v>2017</v>
@@ -1743,7 +1785,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>2018</v>
@@ -1775,7 +1817,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1">
         <v>2019</v>
@@ -1807,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
         <v>2020</v>
@@ -1839,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1">
         <v>2021</v>
@@ -1871,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>2022</v>
@@ -1903,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
         <v>2023</v>
@@ -1935,7 +1977,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>2014</v>
@@ -1967,7 +2009,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>2015</v>
@@ -1999,7 +2041,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>2016</v>
@@ -2031,7 +2073,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>2017</v>
@@ -2063,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>2018</v>
@@ -2095,7 +2137,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1">
         <v>2019</v>
@@ -2127,7 +2169,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <v>2020</v>
@@ -2159,7 +2201,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1">
         <v>2021</v>
@@ -2191,7 +2233,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <v>2022</v>
@@ -2223,7 +2265,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1">
         <v>2023</v>
@@ -2261,200 +2303,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2468,255 +2510,255 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
